--- a/2022 data/excel_outputs/32_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/32_boothwise_data.xlsx
@@ -14,11 +14,80 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="490">
   <si>
     <t>AC 32 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -1162,7 +1231,7 @@
     <t>PRIMARY SCHOOL GANGHETA ROOM 2</t>
   </si>
   <si>
-    <t>PRIMARY SCHOOL ■■■■■■■■</t>
+    <t>PRIMARY SCHOOL GANGHETA ROOM NO. 384</t>
   </si>
   <si>
     <t>PRIMARY SCHOOL BANJARPURI</t>
@@ -1421,8 +1490,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1438,7 +1515,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1446,12 +1523,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1750,82 +1845,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="D2" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="E2" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="F2" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="G2" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="H2" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="I2" t="s">
-        <v>451</v>
+        <v>474</v>
       </c>
       <c r="J2" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="K2" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="L2" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="M2" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="N2" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="O2" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="P2" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="Q2" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="R2" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="S2" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="T2" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="U2" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="V2" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="W2" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="X2" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1833,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1089</v>
@@ -1907,7 +2071,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>1136</v>
@@ -1981,7 +2145,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>985</v>
@@ -2055,7 +2219,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>983</v>
@@ -2129,7 +2293,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>804</v>
@@ -2203,7 +2367,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>891</v>
@@ -2277,7 +2441,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>940</v>
@@ -2351,7 +2515,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>965</v>
@@ -2425,7 +2589,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>971</v>
@@ -2499,7 +2663,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>806</v>
@@ -2573,7 +2737,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>773</v>
@@ -2647,7 +2811,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>1101</v>
@@ -2721,7 +2885,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>1047</v>
@@ -2795,7 +2959,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>1125</v>
@@ -2869,7 +3033,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>1144</v>
@@ -2943,7 +3107,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C18">
         <v>1187</v>
@@ -3017,7 +3181,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>976</v>
@@ -3091,7 +3255,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>794</v>
@@ -3165,7 +3329,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C21">
         <v>743</v>
@@ -3239,7 +3403,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <v>908</v>
@@ -3313,7 +3477,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>1122</v>
@@ -3387,7 +3551,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>1118</v>
@@ -3461,7 +3625,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>1006</v>
@@ -3535,7 +3699,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C26">
         <v>930</v>
@@ -3609,7 +3773,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>773</v>
@@ -3683,7 +3847,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>904</v>
@@ -3757,7 +3921,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>882</v>
@@ -3831,7 +3995,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>1221</v>
@@ -3905,7 +4069,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>916</v>
@@ -3979,7 +4143,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>729</v>
@@ -4053,7 +4217,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>1084</v>
@@ -4127,7 +4291,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>1014</v>
@@ -4201,7 +4365,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>816</v>
@@ -4275,7 +4439,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>682</v>
@@ -4349,7 +4513,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>674</v>
@@ -4423,7 +4587,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>644</v>
@@ -4497,7 +4661,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>1059</v>
@@ -4571,7 +4735,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>842</v>
@@ -4645,7 +4809,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>1190</v>
@@ -4719,7 +4883,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>758</v>
@@ -4793,7 +4957,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>747</v>
@@ -4867,7 +5031,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>606</v>
@@ -4941,7 +5105,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>625</v>
@@ -5015,7 +5179,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>731</v>
@@ -5089,7 +5253,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>781</v>
@@ -5163,7 +5327,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>606</v>
@@ -5237,7 +5401,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>804</v>
@@ -5311,7 +5475,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>752</v>
@@ -5385,7 +5549,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>831</v>
@@ -5459,7 +5623,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>1186</v>
@@ -5533,7 +5697,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>1090</v>
@@ -5607,7 +5771,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>963</v>
@@ -5681,7 +5845,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>876</v>
@@ -5755,7 +5919,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>856</v>
@@ -5829,7 +5993,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>1052</v>
@@ -5903,7 +6067,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>763</v>
@@ -5977,7 +6141,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>687</v>
@@ -6051,7 +6215,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>1049</v>
@@ -6125,7 +6289,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>998</v>
@@ -6199,7 +6363,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>755</v>
@@ -6273,7 +6437,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>994</v>
@@ -6347,7 +6511,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C64">
         <v>802</v>
@@ -6421,7 +6585,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>963</v>
@@ -6495,7 +6659,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>790</v>
@@ -6569,7 +6733,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>908</v>
@@ -6643,7 +6807,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>477</v>
@@ -6717,7 +6881,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>741</v>
@@ -6791,7 +6955,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>1043</v>
@@ -6865,7 +7029,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>1048</v>
@@ -6939,7 +7103,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>1017</v>
@@ -7013,7 +7177,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>675</v>
@@ -7087,7 +7251,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>827</v>
@@ -7161,7 +7325,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>845</v>
@@ -7235,7 +7399,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>878</v>
@@ -7309,7 +7473,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>451</v>
@@ -7383,7 +7547,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>643</v>
@@ -7457,7 +7621,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>600</v>
@@ -7531,7 +7695,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>884</v>
@@ -7605,7 +7769,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>919</v>
@@ -7679,7 +7843,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>779</v>
@@ -7753,7 +7917,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="C83">
         <v>1081</v>
@@ -7827,7 +7991,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>772</v>
@@ -7901,7 +8065,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>431</v>
@@ -7975,7 +8139,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>1062</v>
@@ -8049,7 +8213,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C87">
         <v>479</v>
@@ -8123,7 +8287,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C88">
         <v>903</v>
@@ -8197,7 +8361,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C89">
         <v>1151</v>
@@ -8271,7 +8435,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>589</v>
@@ -8345,7 +8509,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>743</v>
@@ -8419,7 +8583,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C92">
         <v>598</v>
@@ -8493,7 +8657,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>1090</v>
@@ -8567,7 +8731,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C94">
         <v>630</v>
@@ -8641,7 +8805,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C95">
         <v>904</v>
@@ -8715,7 +8879,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C96">
         <v>964</v>
@@ -8789,7 +8953,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C97">
         <v>666</v>
@@ -8863,7 +9027,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C98">
         <v>748</v>
@@ -8937,7 +9101,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C99">
         <v>729</v>
@@ -9011,7 +9175,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>751</v>
@@ -9085,7 +9249,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C101">
         <v>761</v>
@@ -9159,7 +9323,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="C102">
         <v>1164</v>
@@ -9233,7 +9397,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C103">
         <v>1000</v>
@@ -9307,7 +9471,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C104">
         <v>739</v>
@@ -9381,7 +9545,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C105">
         <v>735</v>
@@ -9455,7 +9619,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C106">
         <v>633</v>
@@ -9529,7 +9693,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C107">
         <v>626</v>
@@ -9603,7 +9767,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C108">
         <v>972</v>
@@ -9677,7 +9841,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="C109">
         <v>1107</v>
@@ -9751,7 +9915,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C110">
         <v>800</v>
@@ -9825,7 +9989,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C111">
         <v>579</v>
@@ -9899,7 +10063,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C112">
         <v>914</v>
@@ -9973,7 +10137,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>608</v>
@@ -10047,7 +10211,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="C114">
         <v>754</v>
@@ -10121,7 +10285,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C115">
         <v>632</v>
@@ -10195,7 +10359,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="C116">
         <v>589</v>
@@ -10269,7 +10433,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C117">
         <v>621</v>
@@ -10343,7 +10507,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C118">
         <v>613</v>
@@ -10417,7 +10581,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>488</v>
@@ -10491,7 +10655,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>893</v>
@@ -10565,7 +10729,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>841</v>
@@ -10639,7 +10803,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>1021</v>
@@ -10713,7 +10877,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>1095</v>
@@ -10787,7 +10951,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>754</v>
@@ -10861,7 +11025,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C125">
         <v>703</v>
@@ -10935,7 +11099,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C126">
         <v>1034</v>
@@ -11009,7 +11173,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C127">
         <v>1039</v>
@@ -11083,7 +11247,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C128">
         <v>1037</v>
@@ -11157,7 +11321,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C129">
         <v>1022</v>
@@ -11231,7 +11395,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C130">
         <v>941</v>
@@ -11305,7 +11469,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C131">
         <v>1166</v>
@@ -11379,7 +11543,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C132">
         <v>989</v>
@@ -11453,7 +11617,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="C133">
         <v>1095</v>
@@ -11527,7 +11691,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C134">
         <v>719</v>
@@ -11601,7 +11765,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="C135">
         <v>901</v>
@@ -11675,7 +11839,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="C136">
         <v>824</v>
@@ -11749,7 +11913,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C137">
         <v>954</v>
@@ -11823,7 +11987,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C138">
         <v>632</v>
@@ -11897,7 +12061,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C139">
         <v>593</v>
@@ -11971,7 +12135,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="C140">
         <v>1041</v>
@@ -12045,7 +12209,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C141">
         <v>798</v>
@@ -12119,7 +12283,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C142">
         <v>879</v>
@@ -12193,7 +12357,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="C143">
         <v>888</v>
@@ -12267,7 +12431,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C144">
         <v>756</v>
@@ -12341,7 +12505,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C145">
         <v>1122</v>
@@ -12415,7 +12579,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="C146">
         <v>590</v>
@@ -12489,7 +12653,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C147">
         <v>588</v>
@@ -12563,7 +12727,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C148">
         <v>971</v>
@@ -12637,7 +12801,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C149">
         <v>1025</v>
@@ -12711,7 +12875,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C150">
         <v>715</v>
@@ -12785,7 +12949,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="C151">
         <v>679</v>
@@ -12859,7 +13023,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="C152">
         <v>660</v>
@@ -12933,7 +13097,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="C153">
         <v>622</v>
@@ -13007,7 +13171,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C154">
         <v>941</v>
@@ -13081,7 +13245,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C155">
         <v>794</v>
@@ -13155,7 +13319,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C156">
         <v>671</v>
@@ -13229,7 +13393,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="C157">
         <v>630</v>
@@ -13303,7 +13467,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C158">
         <v>1042</v>
@@ -13377,7 +13541,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C159">
         <v>803</v>
@@ -13451,7 +13615,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C160">
         <v>661</v>
@@ -13525,7 +13689,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C161">
         <v>605</v>
@@ -13599,7 +13763,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C162">
         <v>473</v>
@@ -13673,7 +13837,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C163">
         <v>618</v>
@@ -13747,7 +13911,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C164">
         <v>575</v>
@@ -13821,7 +13985,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C165">
         <v>1057</v>
@@ -13895,7 +14059,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C166">
         <v>976</v>
@@ -13969,7 +14133,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="C167">
         <v>993</v>
@@ -14043,7 +14207,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C168">
         <v>765</v>
@@ -14117,7 +14281,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="C169">
         <v>986</v>
@@ -14191,7 +14355,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C170">
         <v>1058</v>
@@ -14265,7 +14429,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C171">
         <v>952</v>
@@ -14339,7 +14503,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C172">
         <v>1027</v>
@@ -14413,7 +14577,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C173">
         <v>705</v>
@@ -14487,7 +14651,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C174">
         <v>847</v>
@@ -14561,7 +14725,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C175">
         <v>977</v>
@@ -14635,7 +14799,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="C176">
         <v>851</v>
@@ -14709,7 +14873,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C177">
         <v>988</v>
@@ -14783,7 +14947,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="C178">
         <v>729</v>
@@ -14857,7 +15021,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="C179">
         <v>1084</v>
@@ -14931,7 +15095,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C180">
         <v>737</v>
@@ -15005,7 +15169,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C181">
         <v>978</v>
@@ -15079,7 +15243,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="C182">
         <v>386</v>
@@ -15153,7 +15317,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C183">
         <v>1155</v>
@@ -15227,7 +15391,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C184">
         <v>512</v>
@@ -15301,7 +15465,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C185">
         <v>653</v>
@@ -15375,7 +15539,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C186">
         <v>643</v>
@@ -15449,7 +15613,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="C187">
         <v>1144</v>
@@ -15523,7 +15687,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C188">
         <v>977</v>
@@ -15597,7 +15761,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="C189">
         <v>986</v>
@@ -15671,7 +15835,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C190">
         <v>1000</v>
@@ -15745,7 +15909,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C191">
         <v>1189</v>
@@ -15819,7 +15983,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C192">
         <v>1048</v>
@@ -15893,7 +16057,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C193">
         <v>969</v>
@@ -15967,7 +16131,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="C194">
         <v>555</v>
@@ -16041,7 +16205,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="C195">
         <v>1012</v>
@@ -16115,7 +16279,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C196">
         <v>945</v>
@@ -16189,7 +16353,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="C197">
         <v>853</v>
@@ -16263,7 +16427,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="C198">
         <v>785</v>
@@ -16337,7 +16501,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="C199">
         <v>433</v>
@@ -16411,7 +16575,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C200">
         <v>450</v>
@@ -16485,7 +16649,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C201">
         <v>677</v>
@@ -16559,7 +16723,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C202">
         <v>725</v>
@@ -16633,7 +16797,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C203">
         <v>770</v>
@@ -16707,7 +16871,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="C204">
         <v>882</v>
@@ -16781,7 +16945,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C205">
         <v>619</v>
@@ -16855,7 +17019,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C206">
         <v>1150</v>
@@ -16929,7 +17093,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C207">
         <v>1048</v>
@@ -17003,7 +17167,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C208">
         <v>1055</v>
@@ -17077,7 +17241,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C209">
         <v>647</v>
@@ -17151,7 +17315,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="C210">
         <v>636</v>
@@ -17225,7 +17389,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="C211">
         <v>801</v>
@@ -17299,7 +17463,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C212">
         <v>1086</v>
@@ -17373,7 +17537,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="C213">
         <v>1064</v>
@@ -17447,7 +17611,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C214">
         <v>1110</v>
@@ -17521,7 +17685,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="C215">
         <v>675</v>
@@ -17595,7 +17759,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C216">
         <v>572</v>
@@ -17669,7 +17833,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="C217">
         <v>1053</v>
@@ -17743,7 +17907,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="C218">
         <v>969</v>
@@ -17817,7 +17981,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="C219">
         <v>1056</v>
@@ -17891,7 +18055,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C220">
         <v>1033</v>
@@ -17965,7 +18129,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C221">
         <v>711</v>
@@ -18039,7 +18203,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="C222">
         <v>1110</v>
@@ -18113,7 +18277,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C223">
         <v>1177</v>
@@ -18187,7 +18351,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="C224">
         <v>847</v>
@@ -18261,7 +18425,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C225">
         <v>920</v>
@@ -18335,7 +18499,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="C226">
         <v>770</v>
@@ -18409,7 +18573,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C227">
         <v>811</v>
@@ -18483,7 +18647,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="C228">
         <v>875</v>
@@ -18557,7 +18721,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="C229">
         <v>554</v>
@@ -18631,7 +18795,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C230">
         <v>980</v>
@@ -18705,7 +18869,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="C231">
         <v>725</v>
@@ -18779,7 +18943,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C232">
         <v>1096</v>
@@ -18853,7 +19017,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C233">
         <v>931</v>
@@ -18927,7 +19091,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="C234">
         <v>972</v>
@@ -19001,7 +19165,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C235">
         <v>939</v>
@@ -19075,7 +19239,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="C236">
         <v>370</v>
@@ -19149,7 +19313,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="C237">
         <v>748</v>
@@ -19223,7 +19387,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="C238">
         <v>973</v>
@@ -19297,7 +19461,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C239">
         <v>968</v>
@@ -19371,7 +19535,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="C240">
         <v>590</v>
@@ -19445,7 +19609,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="C241">
         <v>935</v>
@@ -19519,7 +19683,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="C242">
         <v>720</v>
@@ -19593,7 +19757,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C243">
         <v>955</v>
@@ -19667,7 +19831,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="C244">
         <v>672</v>
@@ -19741,7 +19905,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C245">
         <v>916</v>
@@ -19815,7 +19979,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="C246">
         <v>1015</v>
@@ -19889,7 +20053,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="C247">
         <v>1095</v>
@@ -19963,7 +20127,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="C248">
         <v>1167</v>
@@ -20037,7 +20201,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="C249">
         <v>777</v>
@@ -20111,7 +20275,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="C250">
         <v>788</v>
@@ -20185,7 +20349,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C251">
         <v>742</v>
@@ -20259,7 +20423,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="C252">
         <v>726</v>
@@ -20333,7 +20497,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="C253">
         <v>516</v>
@@ -20407,7 +20571,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="C254">
         <v>706</v>
@@ -20481,7 +20645,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="C255">
         <v>1052</v>
@@ -20555,7 +20719,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="C256">
         <v>1013</v>
@@ -20629,7 +20793,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="C257">
         <v>719</v>
@@ -20703,7 +20867,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="C258">
         <v>898</v>
@@ -20777,7 +20941,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="C259">
         <v>893</v>
@@ -20851,7 +21015,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="C260">
         <v>783</v>
@@ -20925,7 +21089,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C261">
         <v>724</v>
@@ -20999,7 +21163,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="C262">
         <v>742</v>
@@ -21073,7 +21237,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="C263">
         <v>859</v>
@@ -21147,7 +21311,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="C264">
         <v>909</v>
@@ -21221,7 +21385,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="C265">
         <v>776</v>
@@ -21295,7 +21459,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="C266">
         <v>958</v>
@@ -21369,7 +21533,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="C267">
         <v>903</v>
@@ -21443,7 +21607,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C268">
         <v>800</v>
@@ -21517,7 +21681,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="C269">
         <v>1133</v>
@@ -21591,7 +21755,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="C270">
         <v>1127</v>
@@ -21665,7 +21829,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="C271">
         <v>1066</v>
@@ -21739,7 +21903,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="C272">
         <v>989</v>
@@ -21813,7 +21977,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C273">
         <v>1036</v>
@@ -21887,7 +22051,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="C274">
         <v>1032</v>
@@ -21961,7 +22125,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="C275">
         <v>1074</v>
@@ -22035,7 +22199,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="C276">
         <v>966</v>
@@ -22109,7 +22273,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="C277">
         <v>955</v>
@@ -22183,7 +22347,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="C278">
         <v>1002</v>
@@ -22257,7 +22421,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="C279">
         <v>922</v>
@@ -22331,7 +22495,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="C280">
         <v>752</v>
@@ -22405,7 +22569,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="C281">
         <v>963</v>
@@ -22479,7 +22643,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="C282">
         <v>921</v>
@@ -22553,7 +22717,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="C283">
         <v>532</v>
@@ -22627,7 +22791,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="C284">
         <v>928</v>
@@ -22701,7 +22865,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="C285">
         <v>727</v>
@@ -22775,7 +22939,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="C286">
         <v>719</v>
@@ -22849,7 +23013,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="C287">
         <v>795</v>
@@ -22923,7 +23087,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="C288">
         <v>978</v>
@@ -22997,7 +23161,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="C289">
         <v>545</v>
@@ -23071,7 +23235,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="C290">
         <v>961</v>
@@ -23145,7 +23309,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="C291">
         <v>665</v>
@@ -23219,7 +23383,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="C292">
         <v>670</v>
@@ -23293,7 +23457,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="C293">
         <v>667</v>
@@ -23367,7 +23531,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="C294">
         <v>556</v>
@@ -23441,7 +23605,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="C295">
         <v>794</v>
@@ -23515,7 +23679,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="C296">
         <v>985</v>
@@ -23589,7 +23753,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="C297">
         <v>809</v>
@@ -23663,7 +23827,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C298">
         <v>677</v>
@@ -23737,7 +23901,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="C299">
         <v>668</v>
@@ -23811,7 +23975,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="C300">
         <v>962</v>
@@ -23885,7 +24049,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C301">
         <v>775</v>
@@ -23959,7 +24123,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="C302">
         <v>1066</v>
@@ -24033,7 +24197,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="C303">
         <v>644</v>
@@ -24107,7 +24271,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="C304">
         <v>647</v>
@@ -24181,7 +24345,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="C305">
         <v>979</v>
@@ -24255,7 +24419,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="C306">
         <v>1134</v>
@@ -24329,7 +24493,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="C307">
         <v>1028</v>
@@ -24403,7 +24567,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C308">
         <v>992</v>
@@ -24477,7 +24641,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="C309">
         <v>1031</v>
@@ -24551,7 +24715,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C310">
         <v>811</v>
@@ -24625,7 +24789,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C311">
         <v>1160</v>
@@ -24699,7 +24863,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="C312">
         <v>738</v>
@@ -24773,7 +24937,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="C313">
         <v>939</v>
@@ -24847,7 +25011,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C314">
         <v>909</v>
@@ -24921,7 +25085,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="C315">
         <v>889</v>
@@ -24995,7 +25159,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="C316">
         <v>757</v>
@@ -25069,7 +25233,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C317">
         <v>838</v>
@@ -25143,7 +25307,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C318">
         <v>744</v>
@@ -25217,7 +25381,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C319">
         <v>1205</v>
@@ -25291,7 +25455,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="C320">
         <v>847</v>
@@ -25365,7 +25529,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C321">
         <v>940</v>
@@ -25439,7 +25603,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C322">
         <v>625</v>
@@ -25513,7 +25677,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="C323">
         <v>960</v>
@@ -25587,7 +25751,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="C324">
         <v>970</v>
@@ -25661,7 +25825,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="C325">
         <v>740</v>
@@ -25735,7 +25899,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="C326">
         <v>1054</v>
@@ -25809,7 +25973,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="C327">
         <v>672</v>
@@ -25883,7 +26047,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="C328">
         <v>1028</v>
@@ -25957,7 +26121,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="C329">
         <v>1053</v>
@@ -26031,7 +26195,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="C330">
         <v>943</v>
@@ -26105,7 +26269,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="C331">
         <v>878</v>
@@ -26179,7 +26343,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="C332">
         <v>937</v>
@@ -26253,7 +26417,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="C333">
         <v>931</v>
@@ -26327,7 +26491,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="C334">
         <v>760</v>
@@ -26401,7 +26565,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="C335">
         <v>757</v>
@@ -26475,7 +26639,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="C336">
         <v>726</v>
@@ -26549,7 +26713,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="C337">
         <v>1021</v>
@@ -26623,7 +26787,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="C338">
         <v>754</v>
@@ -26697,7 +26861,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="C339">
         <v>715</v>
@@ -26771,7 +26935,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="C340">
         <v>888</v>
@@ -26845,7 +27009,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C341">
         <v>840</v>
@@ -26919,7 +27083,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="C342">
         <v>734</v>
@@ -26993,7 +27157,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="C343">
         <v>1086</v>
@@ -27067,7 +27231,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="C344">
         <v>742</v>
@@ -27141,7 +27305,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="C345">
         <v>892</v>
@@ -27215,7 +27379,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="C346">
         <v>1060</v>
@@ -27289,7 +27453,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C347">
         <v>1023</v>
@@ -27363,7 +27527,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="C348">
         <v>1122</v>
@@ -27437,7 +27601,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="C349">
         <v>694</v>
@@ -27511,7 +27675,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="C350">
         <v>719</v>
@@ -27585,7 +27749,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="C351">
         <v>720</v>
@@ -27659,7 +27823,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="C352">
         <v>683</v>
@@ -27733,7 +27897,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="C353">
         <v>1147</v>
@@ -27807,7 +27971,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="C354">
         <v>1161</v>
@@ -27881,7 +28045,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="C355">
         <v>705</v>
@@ -27955,7 +28119,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="C356">
         <v>652</v>
@@ -28029,7 +28193,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="C357">
         <v>896</v>
@@ -28103,7 +28267,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="C358">
         <v>628</v>
@@ -28177,7 +28341,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C359">
         <v>1203</v>
@@ -28251,7 +28415,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="C360">
         <v>791</v>
@@ -28325,7 +28489,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="C361">
         <v>621</v>
@@ -28399,7 +28563,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="C362">
         <v>622</v>
@@ -28473,7 +28637,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="C363">
         <v>939</v>
@@ -28547,7 +28711,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="C364">
         <v>1071</v>
@@ -28621,7 +28785,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="C365">
         <v>965</v>
@@ -28695,7 +28859,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="C366">
         <v>910</v>
@@ -28769,7 +28933,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="C367">
         <v>1030</v>
@@ -28843,7 +29007,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="C368">
         <v>930</v>
@@ -28917,7 +29081,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="C369">
         <v>820</v>
@@ -28991,7 +29155,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="C370">
         <v>658</v>
@@ -29065,7 +29229,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="C371">
         <v>628</v>
@@ -29139,7 +29303,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="C372">
         <v>969</v>
@@ -29213,7 +29377,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="C373">
         <v>1142</v>
@@ -29287,7 +29451,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="C374">
         <v>938</v>
@@ -29361,7 +29525,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="C375">
         <v>593</v>
@@ -29435,7 +29599,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="C376">
         <v>848</v>
@@ -29509,7 +29673,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="C377">
         <v>389</v>
@@ -29583,7 +29747,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="C378">
         <v>1138</v>
@@ -29657,7 +29821,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="C379">
         <v>778</v>
@@ -29731,7 +29895,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="C380">
         <v>1205</v>
@@ -29805,7 +29969,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="C381">
         <v>631</v>
@@ -29879,7 +30043,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="C382">
         <v>728</v>
@@ -29953,7 +30117,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="C383">
         <v>688</v>
@@ -30027,7 +30191,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="C384">
         <v>610</v>
@@ -30101,7 +30265,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="C385">
         <v>596</v>
@@ -30175,7 +30339,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="C386">
         <v>520</v>
@@ -30249,7 +30413,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="C387">
         <v>568</v>
@@ -30323,7 +30487,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="C388">
         <v>1017</v>
@@ -30397,7 +30561,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="C389">
         <v>1001</v>
@@ -30471,7 +30635,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="C390">
         <v>1048</v>
@@ -30545,7 +30709,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="C391">
         <v>976</v>
@@ -30619,7 +30783,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="C392">
         <v>1055</v>
@@ -30693,7 +30857,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="C393">
         <v>1030</v>
@@ -30767,7 +30931,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="C394">
         <v>1045</v>
@@ -30841,7 +31005,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="C395">
         <v>1050</v>
@@ -30915,7 +31079,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="C396">
         <v>821</v>
@@ -30989,7 +31153,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="C397">
         <v>804</v>
@@ -31063,7 +31227,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="C398">
         <v>1073</v>
@@ -31137,7 +31301,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="C399">
         <v>1152</v>
@@ -31211,7 +31375,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="C400">
         <v>498</v>
@@ -31285,7 +31449,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="C401">
         <v>795</v>
@@ -31359,7 +31523,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="C402">
         <v>682</v>
@@ -31433,7 +31597,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="C403">
         <v>652</v>
@@ -31507,7 +31671,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="C404">
         <v>646</v>
@@ -31581,7 +31745,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="C405">
         <v>632</v>
@@ -31655,7 +31819,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="C406">
         <v>989</v>
@@ -31729,7 +31893,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="C407">
         <v>868</v>
@@ -31803,7 +31967,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="C408">
         <v>345</v>
@@ -31877,7 +32041,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="C409">
         <v>536</v>
@@ -31951,7 +32115,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="C410">
         <v>663</v>
@@ -32025,7 +32189,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="C411">
         <v>633</v>
@@ -32099,7 +32263,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="C412">
         <v>910</v>
@@ -32173,7 +32337,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="C413">
         <v>900</v>
@@ -32247,7 +32411,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="C414">
         <v>909</v>
@@ -32321,7 +32485,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="C415">
         <v>601</v>
@@ -32395,7 +32559,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="C416">
         <v>782</v>
@@ -32469,7 +32633,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="C417">
         <v>671</v>
@@ -32543,7 +32707,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="C418">
         <v>952</v>
@@ -32617,7 +32781,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="C419">
         <v>757</v>
@@ -32691,7 +32855,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="C420">
         <v>1072</v>
@@ -32765,7 +32929,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="C421">
         <v>933</v>
@@ -32839,7 +33003,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="C422">
         <v>964</v>
@@ -32913,7 +33077,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="C423">
         <v>778</v>
@@ -32987,7 +33151,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="C424">
         <v>527</v>
@@ -33061,7 +33225,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="C425">
         <v>901</v>
@@ -33135,7 +33299,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="C426">
         <v>949</v>
@@ -33209,7 +33373,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="C427">
         <v>831</v>
@@ -33283,7 +33447,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="C428">
         <v>583</v>
@@ -33357,7 +33521,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="C429">
         <v>1153</v>
@@ -33431,7 +33595,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="C430">
         <v>517</v>
@@ -33505,7 +33669,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="C431">
         <v>671</v>
@@ -33579,7 +33743,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="C432">
         <v>577</v>
@@ -33653,7 +33817,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="C433">
         <v>987</v>
@@ -33727,7 +33891,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="C434">
         <v>641</v>
@@ -33801,7 +33965,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="C435">
         <v>612</v>
@@ -33875,7 +34039,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="C436">
         <v>1012</v>
@@ -33949,7 +34113,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="C437">
         <v>670</v>
@@ -34023,7 +34187,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>434</v>
+        <v>457</v>
       </c>
       <c r="C438">
         <v>1142</v>
@@ -34097,7 +34261,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="C439">
         <v>912</v>
@@ -34171,7 +34335,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="C440">
         <v>715</v>
@@ -34245,7 +34409,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="C441">
         <v>871</v>
@@ -34319,7 +34483,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="C442">
         <v>821</v>
@@ -34393,7 +34557,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="C443">
         <v>836</v>
@@ -34467,7 +34631,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="C444">
         <v>954</v>
@@ -34541,7 +34705,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="C445">
         <v>937</v>
@@ -34615,7 +34779,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="C446">
         <v>606</v>
@@ -34689,7 +34853,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="C447">
         <v>599</v>
@@ -34763,7 +34927,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="C448">
         <v>1001</v>
